--- a/02-Test-Cases/FB_SignUp_TestCases.xlsx
+++ b/02-Test-Cases/FB_SignUp_TestCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ql3ql\Desktop\Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ql3ql\Desktop\resume\Review\Test-Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A318ED4D-8585-4563-A78F-0FA0BDE20455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60788B9-C28D-4F32-A31B-D7FA617237BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -759,7 +759,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -796,12 +796,6 @@
         <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -815,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -880,22 +874,15 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -903,7 +890,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,7 +1412,7 @@
       <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -1441,8 +1428,8 @@
       <c r="B5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="10"/>
       <c r="F5" s="11"/>
     </row>
@@ -1453,8 +1440,8 @@
       <c r="B6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
     </row>
@@ -1465,8 +1452,8 @@
       <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="10"/>
       <c r="F7" s="11"/>
     </row>
@@ -1477,8 +1464,8 @@
       <c r="B8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
     </row>
@@ -1489,8 +1476,8 @@
       <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
     </row>
@@ -1501,8 +1488,8 @@
       <c r="B10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
     </row>
@@ -1513,8 +1500,8 @@
       <c r="B11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
@@ -1540,7 +1527,7 @@
       <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="23" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="25" t="s">
@@ -1556,8 +1543,8 @@
       <c r="B14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
     </row>
@@ -1568,8 +1555,8 @@
       <c r="B15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="10"/>
       <c r="F15" s="11"/>
     </row>
@@ -1580,8 +1567,8 @@
       <c r="B16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="10"/>
       <c r="F16" s="11"/>
     </row>
@@ -1592,8 +1579,8 @@
       <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
     </row>
@@ -1604,8 +1591,8 @@
       <c r="B18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="10"/>
       <c r="F18" s="11"/>
     </row>
@@ -1616,8 +1603,8 @@
       <c r="B19" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
       <c r="E19" s="10"/>
       <c r="F19" s="11"/>
     </row>
@@ -1628,8 +1615,8 @@
       <c r="B20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
       <c r="E20" s="10"/>
       <c r="F20" s="11"/>
     </row>
@@ -1655,7 +1642,7 @@
       <c r="B22" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="23" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="25" t="s">
@@ -1668,11 +1655,11 @@
       <c r="A23" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="10"/>
       <c r="F23" s="11"/>
     </row>
@@ -1680,11 +1667,11 @@
       <c r="A24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
       <c r="E24" s="10"/>
       <c r="F24" s="11"/>
     </row>
@@ -1695,8 +1682,8 @@
       <c r="B25" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
       <c r="E25" s="10"/>
       <c r="F25" s="11"/>
     </row>
@@ -1707,8 +1694,8 @@
       <c r="B26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
     </row>
@@ -1719,8 +1706,8 @@
       <c r="B27" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
       <c r="E27" s="10"/>
       <c r="F27" s="11"/>
     </row>
@@ -1731,8 +1718,8 @@
       <c r="B28" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="10"/>
       <c r="F28" s="11"/>
     </row>
@@ -1743,8 +1730,8 @@
       <c r="B29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="10"/>
       <c r="F29" s="11"/>
     </row>
@@ -1770,7 +1757,7 @@
       <c r="B31" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="23" t="s">
         <v>42</v>
       </c>
       <c r="D31" s="25" t="s">
@@ -1786,8 +1773,8 @@
       <c r="B32" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
       <c r="E32" s="10"/>
       <c r="F32" s="11"/>
     </row>
@@ -1798,8 +1785,8 @@
       <c r="B33" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
       <c r="E33" s="10"/>
       <c r="F33" s="11"/>
     </row>
@@ -1810,8 +1797,8 @@
       <c r="B34" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
       <c r="E34" s="10"/>
       <c r="F34" s="11"/>
     </row>
@@ -1822,8 +1809,8 @@
       <c r="B35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
       <c r="E35" s="10"/>
       <c r="F35" s="11"/>
     </row>
@@ -1834,8 +1821,8 @@
       <c r="B36" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
       <c r="E36" s="10"/>
       <c r="F36" s="11"/>
     </row>
@@ -1846,8 +1833,8 @@
       <c r="B37" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
       <c r="E37" s="10"/>
       <c r="F37" s="11"/>
     </row>
@@ -1858,8 +1845,8 @@
       <c r="B38" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
       <c r="E38" s="10"/>
       <c r="F38" s="11"/>
     </row>
@@ -1885,7 +1872,7 @@
       <c r="B40" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="23" t="s">
         <v>65</v>
       </c>
       <c r="D40" s="25" t="s">
@@ -1901,8 +1888,8 @@
       <c r="B41" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
       <c r="E41" s="10"/>
       <c r="F41" s="11"/>
     </row>
@@ -1913,8 +1900,8 @@
       <c r="B42" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
       <c r="E42" s="10"/>
       <c r="F42" s="11"/>
     </row>
@@ -1925,8 +1912,8 @@
       <c r="B43" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
       <c r="E43" s="10"/>
       <c r="F43" s="11"/>
     </row>
@@ -1937,8 +1924,8 @@
       <c r="B44" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
       <c r="E44" s="10"/>
       <c r="F44" s="11"/>
     </row>
@@ -1964,7 +1951,7 @@
       <c r="B46" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="25" t="s">
@@ -1980,8 +1967,8 @@
       <c r="B47" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
       <c r="E47" s="10"/>
       <c r="F47" s="11"/>
     </row>
@@ -1992,8 +1979,8 @@
       <c r="B48" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
       <c r="E48" s="10"/>
       <c r="F48" s="11"/>
     </row>
@@ -2004,8 +1991,8 @@
       <c r="B49" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
       <c r="E49" s="10"/>
       <c r="F49" s="11"/>
     </row>
@@ -2031,7 +2018,7 @@
       <c r="B51" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D51" s="25" t="s">
@@ -2047,8 +2034,8 @@
       <c r="B52" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
       <c r="E52" s="10"/>
       <c r="F52" s="11"/>
     </row>
@@ -2059,8 +2046,8 @@
       <c r="B53" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
       <c r="E53" s="10"/>
       <c r="F53" s="11"/>
     </row>
@@ -2071,8 +2058,8 @@
       <c r="B54" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
       <c r="E54" s="10"/>
       <c r="F54" s="11"/>
     </row>
@@ -2098,7 +2085,7 @@
       <c r="B56" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="C56" s="23" t="s">
         <v>87</v>
       </c>
       <c r="D56" s="25" t="s">
@@ -2114,8 +2101,8 @@
       <c r="B57" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
       <c r="E57" s="10"/>
       <c r="F57" s="11"/>
     </row>
@@ -2126,8 +2113,8 @@
       <c r="B58" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
       <c r="E58" s="10"/>
       <c r="F58" s="11"/>
     </row>
@@ -2138,8 +2125,8 @@
       <c r="B59" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
       <c r="E59" s="10"/>
       <c r="F59" s="11"/>
     </row>
@@ -2165,7 +2152,7 @@
       <c r="B61" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="23" t="s">
         <v>87</v>
       </c>
       <c r="D61" s="25" t="s">
@@ -2181,8 +2168,8 @@
       <c r="B62" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
       <c r="E62" s="10"/>
       <c r="F62" s="11"/>
     </row>
@@ -2193,8 +2180,8 @@
       <c r="B63" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
       <c r="E63" s="10"/>
       <c r="F63" s="11"/>
     </row>
@@ -2205,8 +2192,8 @@
       <c r="B64" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
       <c r="E64" s="10"/>
       <c r="F64" s="11"/>
     </row>
@@ -2232,7 +2219,7 @@
       <c r="B66" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C66" s="27" t="s">
+      <c r="C66" s="23" t="s">
         <v>87</v>
       </c>
       <c r="D66" s="25" t="s">
@@ -2248,8 +2235,8 @@
       <c r="B67" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
       <c r="E67" s="10"/>
       <c r="F67" s="11"/>
     </row>
@@ -2260,8 +2247,8 @@
       <c r="B68" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
       <c r="E68" s="10"/>
       <c r="F68" s="11"/>
     </row>
@@ -2272,8 +2259,8 @@
       <c r="B69" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
       <c r="E69" s="10"/>
       <c r="F69" s="11"/>
     </row>
@@ -2299,7 +2286,7 @@
       <c r="B71" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C71" s="27" t="s">
+      <c r="C71" s="23" t="s">
         <v>87</v>
       </c>
       <c r="D71" s="25" t="s">
@@ -2315,8 +2302,8 @@
       <c r="B72" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
       <c r="E72" s="10"/>
       <c r="F72" s="11"/>
     </row>
@@ -2327,8 +2314,8 @@
       <c r="B73" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
       <c r="E73" s="10"/>
       <c r="F73" s="11"/>
     </row>
@@ -2339,8 +2326,8 @@
       <c r="B74" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
       <c r="E74" s="10"/>
       <c r="F74" s="11"/>
     </row>
@@ -2460,6 +2447,14 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D31:D38"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="D4:D11"/>
+    <mergeCell ref="C13:C20"/>
+    <mergeCell ref="D13:D20"/>
+    <mergeCell ref="C22:C29"/>
+    <mergeCell ref="D22:D29"/>
+    <mergeCell ref="C31:C38"/>
     <mergeCell ref="C61:C64"/>
     <mergeCell ref="C66:C69"/>
     <mergeCell ref="C71:C74"/>
@@ -2474,14 +2469,6 @@
     <mergeCell ref="C46:C49"/>
     <mergeCell ref="C51:C54"/>
     <mergeCell ref="C56:C59"/>
-    <mergeCell ref="D31:D38"/>
-    <mergeCell ref="C4:C11"/>
-    <mergeCell ref="D4:D11"/>
-    <mergeCell ref="C13:C20"/>
-    <mergeCell ref="D13:D20"/>
-    <mergeCell ref="C22:C29"/>
-    <mergeCell ref="D22:D29"/>
-    <mergeCell ref="C31:C38"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D4:D11 D13:D20 D22:D76 F30 F39 F45 F50 F55 F60 F65 F70 F75:F76">
@@ -2531,7 +2518,7 @@
     <tabColor rgb="FF6AA84F"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -2540,10 +2527,9 @@
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2562,9 +2548,8 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -2573,9 +2558,8 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6">
+    </row>
+    <row r="3" spans="1:6" ht="15.6">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -2588,16 +2572,15 @@
       <c r="F3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="23" t="s">
         <v>113</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -2606,31 +2589,31 @@
       <c r="E4" s="10"/>
       <c r="F4" s="11"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="10"/>
       <c r="F5" s="11"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:7" ht="15.6">
+    <row r="7" spans="1:6" ht="15.6">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -2643,16 +2626,15 @@
       <c r="F7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="23" t="s">
         <v>118</v>
       </c>
       <c r="D8" s="25" t="s">
@@ -2661,31 +2643,31 @@
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:6">
       <c r="A10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="15.6">
+    <row r="11" spans="1:6" ht="15.6">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -2698,16 +2680,15 @@
       <c r="F11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7">
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="23" t="s">
         <v>121</v>
       </c>
       <c r="D12" s="25" t="s">
@@ -2716,31 +2697,31 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:6">
       <c r="A14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="15.6">
+    <row r="15" spans="1:6" ht="15.6">
       <c r="A15" s="5">
         <v>4</v>
       </c>
@@ -2753,16 +2734,15 @@
       <c r="F15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7">
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="23" t="s">
         <v>124</v>
       </c>
       <c r="D16" s="25" t="s">
@@ -2771,31 +2751,31 @@
       <c r="E16" s="10"/>
       <c r="F16" s="11"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="10"/>
       <c r="F18" s="11"/>
     </row>
-    <row r="19" spans="1:7" ht="15.6">
+    <row r="19" spans="1:6" ht="15.6">
       <c r="A19" s="5">
         <v>5</v>
       </c>
@@ -2808,16 +2788,15 @@
       <c r="F19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7">
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="23" t="s">
         <v>127</v>
       </c>
       <c r="D20" s="25" t="s">
@@ -2826,31 +2805,31 @@
       <c r="E20" s="10"/>
       <c r="F20" s="11"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
       <c r="E22" s="10"/>
       <c r="F22" s="11"/>
     </row>
-    <row r="23" spans="1:7" ht="15.6">
+    <row r="23" spans="1:6" ht="15.6">
       <c r="A23" s="5">
         <v>6</v>
       </c>
@@ -2861,18 +2840,17 @@
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="8" t="s">
         <v>74</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="23" t="s">
         <v>130</v>
       </c>
       <c r="D24" s="25" t="s">
@@ -2881,31 +2859,31 @@
       <c r="E24" s="10"/>
       <c r="F24" s="11"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:6">
       <c r="A25" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
       <c r="E25" s="10"/>
       <c r="F25" s="11"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:6">
       <c r="A26" s="8" t="s">
         <v>77</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:6" ht="15.6">
       <c r="A27" s="5">
         <v>7</v>
       </c>
@@ -2916,18 +2894,17 @@
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="8" t="s">
         <v>80</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="23" t="s">
         <v>133</v>
       </c>
       <c r="D28" s="25" t="s">
@@ -2936,31 +2913,31 @@
       <c r="E28" s="10"/>
       <c r="F28" s="11"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:6">
       <c r="A29" s="8" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="10"/>
       <c r="F29" s="11"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:6">
       <c r="A30" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
       <c r="E30" s="10"/>
       <c r="F30" s="11"/>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:6" ht="15.6">
       <c r="A31" s="15">
         <v>8</v>
       </c>
@@ -2971,54 +2948,50 @@
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="16"/>
-    </row>
-    <row r="32" spans="1:7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="18" t="s">
         <v>86</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="27" t="s">
         <v>137</v>
       </c>
       <c r="E32" s="20"/>
       <c r="F32" s="21"/>
-      <c r="G32" s="22"/>
-    </row>
-    <row r="33" spans="1:7">
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
       <c r="E33" s="20"/>
       <c r="F33" s="21"/>
-      <c r="G33" s="22"/>
-    </row>
-    <row r="34" spans="1:7">
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="18" t="s">
         <v>90</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
       <c r="E34" s="20"/>
       <c r="F34" s="21"/>
-      <c r="G34" s="22"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.6">
+    </row>
+    <row r="35" spans="1:6" ht="15.6">
       <c r="A35" s="5">
         <v>9</v>
       </c>
@@ -3029,18 +3002,17 @@
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C36" s="23" t="s">
         <v>140</v>
       </c>
       <c r="D36" s="25" t="s">
@@ -3049,31 +3021,31 @@
       <c r="E36" s="10"/>
       <c r="F36" s="11"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:6">
       <c r="A37" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
       <c r="E37" s="10"/>
       <c r="F37" s="11"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:6">
       <c r="A38" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
       <c r="E38" s="10"/>
       <c r="F38" s="11"/>
     </row>
-    <row r="39" spans="1:7" ht="15.6">
+    <row r="39" spans="1:6" ht="15.6">
       <c r="A39" s="5">
         <v>10</v>
       </c>
@@ -3084,18 +3056,17 @@
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="23" t="s">
         <v>143</v>
       </c>
       <c r="D40" s="25" t="s">
@@ -3104,31 +3075,31 @@
       <c r="E40" s="10"/>
       <c r="F40" s="11"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:6">
       <c r="A41" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
       <c r="E41" s="10"/>
       <c r="F41" s="11"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:6">
       <c r="A42" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
       <c r="E42" s="10"/>
       <c r="F42" s="11"/>
     </row>
-    <row r="43" spans="1:7" ht="31.2">
+    <row r="43" spans="1:6" ht="31.2">
       <c r="A43" s="5">
         <v>11</v>
       </c>
@@ -3139,18 +3110,17 @@
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="27" t="s">
+      <c r="C44" s="23" t="s">
         <v>146</v>
       </c>
       <c r="D44" s="25" t="s">
@@ -3159,31 +3129,31 @@
       <c r="E44" s="10"/>
       <c r="F44" s="11"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:6">
       <c r="A45" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
       <c r="E45" s="10"/>
       <c r="F45" s="11"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:6">
       <c r="A46" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
       <c r="E46" s="10"/>
       <c r="F46" s="11"/>
     </row>
-    <row r="47" spans="1:7" ht="31.2">
+    <row r="47" spans="1:6" ht="31.2">
       <c r="A47" s="5">
         <v>12</v>
       </c>
@@ -3194,18 +3164,17 @@
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C48" s="23" t="s">
         <v>146</v>
       </c>
       <c r="D48" s="25" t="s">
@@ -3214,31 +3183,31 @@
       <c r="E48" s="10"/>
       <c r="F48" s="11"/>
     </row>
-    <row r="49" spans="1:7" ht="26.4">
+    <row r="49" spans="1:6" ht="26.4">
       <c r="A49" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
       <c r="E49" s="10"/>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:6">
       <c r="A50" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
       <c r="E50" s="10"/>
       <c r="F50" s="11"/>
     </row>
-    <row r="51" spans="1:7" ht="15.6">
+    <row r="51" spans="1:6" ht="15.6">
       <c r="A51" s="5">
         <v>13</v>
       </c>
@@ -3249,18 +3218,17 @@
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" s="6"/>
-    </row>
-    <row r="52" spans="1:7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="23" t="s">
         <v>146</v>
       </c>
       <c r="D52" s="25" t="s">
@@ -3271,31 +3239,31 @@
       </c>
       <c r="F52" s="11"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:6">
       <c r="A53" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
       <c r="F53" s="11"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:6">
       <c r="A54" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
       <c r="F54" s="11"/>
     </row>
-    <row r="55" spans="1:7" ht="31.2">
+    <row r="55" spans="1:6" ht="31.2">
       <c r="A55" s="5">
         <v>14</v>
       </c>
@@ -3306,18 +3274,17 @@
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="6"/>
-    </row>
-    <row r="56" spans="1:7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="C56" s="23" t="s">
         <v>146</v>
       </c>
       <c r="D56" s="25" t="s">
@@ -3326,31 +3293,31 @@
       <c r="E56" s="10"/>
       <c r="F56" s="11"/>
     </row>
-    <row r="57" spans="1:7" ht="26.4">
+    <row r="57" spans="1:6" ht="26.4">
       <c r="A57" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
       <c r="E57" s="10"/>
       <c r="F57" s="11"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:6">
       <c r="A58" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
       <c r="E58" s="10"/>
       <c r="F58" s="11"/>
     </row>
-    <row r="59" spans="1:7" ht="31.2">
+    <row r="59" spans="1:6" ht="31.2">
       <c r="A59" s="5">
         <v>15</v>
       </c>
@@ -3361,18 +3328,17 @@
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G59" s="6"/>
-    </row>
-    <row r="60" spans="1:7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="23" t="s">
         <v>146</v>
       </c>
       <c r="D60" s="25" t="s">
@@ -3383,31 +3349,31 @@
       </c>
       <c r="F60" s="11"/>
     </row>
-    <row r="61" spans="1:7" ht="26.4">
+    <row r="61" spans="1:6" ht="26.4">
       <c r="A61" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
       <c r="F61" s="11"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:6">
       <c r="A62" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
       <c r="F62" s="11"/>
     </row>
-    <row r="63" spans="1:7" ht="31.2">
+    <row r="63" spans="1:6" ht="31.2">
       <c r="A63" s="5">
         <v>16</v>
       </c>
@@ -3420,16 +3386,15 @@
       <c r="F63" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G63" s="6"/>
-    </row>
-    <row r="64" spans="1:7">
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C64" s="23" t="s">
         <v>159</v>
       </c>
       <c r="D64" s="25" t="s">
@@ -3438,31 +3403,31 @@
       <c r="E64" s="10"/>
       <c r="F64" s="11"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:6">
       <c r="A65" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
       <c r="E65" s="10"/>
       <c r="F65" s="11"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:6">
       <c r="A66" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
       <c r="E66" s="10"/>
       <c r="F66" s="11"/>
     </row>
-    <row r="67" spans="1:7" ht="31.2">
+    <row r="67" spans="1:6" ht="31.2">
       <c r="A67" s="5">
         <v>17</v>
       </c>
@@ -3475,16 +3440,15 @@
       <c r="F67" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="6"/>
-    </row>
-    <row r="68" spans="1:7">
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="27" t="s">
+      <c r="C68" s="23" t="s">
         <v>159</v>
       </c>
       <c r="D68" s="25" t="s">
@@ -3495,31 +3459,31 @@
       </c>
       <c r="F68" s="11"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:6">
       <c r="A69" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
       <c r="F69" s="11"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:6">
       <c r="A70" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="11"/>
     </row>
-    <row r="71" spans="1:7" ht="31.2">
+    <row r="71" spans="1:6" ht="31.2">
       <c r="A71" s="5">
         <v>18</v>
       </c>
@@ -3532,16 +3496,15 @@
       <c r="F71" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G71" s="6"/>
-    </row>
-    <row r="72" spans="1:7">
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="C72" s="23" t="s">
         <v>159</v>
       </c>
       <c r="D72" s="25" t="s">
@@ -3552,31 +3515,31 @@
       </c>
       <c r="F72" s="11"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:6">
       <c r="A73" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
       <c r="F73" s="11"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:6">
       <c r="A74" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
       <c r="F74" s="11"/>
     </row>
-    <row r="75" spans="1:7" ht="31.2">
+    <row r="75" spans="1:6" ht="31.2">
       <c r="A75" s="5">
         <v>19</v>
       </c>
@@ -3589,16 +3552,15 @@
       <c r="F75" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G75" s="6"/>
-    </row>
-    <row r="76" spans="1:7">
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="C76" s="23" t="s">
         <v>159</v>
       </c>
       <c r="D76" s="25" t="s">
@@ -3609,31 +3571,31 @@
       </c>
       <c r="F76" s="11"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:6">
       <c r="A77" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
       <c r="F77" s="11"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:6">
       <c r="A78" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
       <c r="F78" s="11"/>
     </row>
-    <row r="79" spans="1:7" ht="15.6">
+    <row r="79" spans="1:6" ht="15.6">
       <c r="A79" s="5">
         <v>20</v>
       </c>
@@ -3646,16 +3608,15 @@
       <c r="F79" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G79" s="6"/>
-    </row>
-    <row r="80" spans="1:7">
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C80" s="27" t="s">
+      <c r="C80" s="23" t="s">
         <v>168</v>
       </c>
       <c r="D80" s="25" t="s">
@@ -3664,31 +3625,31 @@
       <c r="E80" s="10"/>
       <c r="F80" s="11"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:6">
       <c r="A81" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
       <c r="E81" s="10"/>
       <c r="F81" s="11"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:6">
       <c r="A82" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="24"/>
       <c r="E82" s="10"/>
       <c r="F82" s="11"/>
     </row>
-    <row r="83" spans="1:7" ht="15.6">
+    <row r="83" spans="1:6" ht="15.6">
       <c r="A83" s="5">
         <v>21</v>
       </c>
@@ -3701,16 +3662,15 @@
       <c r="F83" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G83" s="6"/>
-    </row>
-    <row r="84" spans="1:7">
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C84" s="27" t="s">
+      <c r="C84" s="23" t="s">
         <v>168</v>
       </c>
       <c r="D84" s="25" t="s">
@@ -3721,87 +3681,67 @@
       </c>
       <c r="F84" s="11"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:6">
       <c r="A85" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="24"/>
+      <c r="E85" s="24"/>
       <c r="F85" s="11"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:6">
       <c r="A86" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C86" s="26"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="26"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="24"/>
+      <c r="E86" s="24"/>
       <c r="F86" s="11"/>
     </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="8"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="13"/>
+    <row r="87" spans="1:6">
+      <c r="C87" s="13"/>
+      <c r="D87" s="10"/>
       <c r="E87" s="10"/>
       <c r="F87" s="11"/>
     </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="8"/>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="13"/>
+    <row r="88" spans="1:6">
+      <c r="C88" s="13"/>
+      <c r="D88" s="10"/>
       <c r="E88" s="10"/>
       <c r="F88" s="11"/>
     </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="8"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="13"/>
+    <row r="89" spans="1:6">
+      <c r="C89" s="13"/>
+      <c r="D89" s="10"/>
       <c r="E89" s="10"/>
       <c r="F89" s="11"/>
     </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="8"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="10"/>
+    <row r="90" spans="1:6">
       <c r="F90" s="11"/>
     </row>
-    <row r="91" spans="1:7">
-      <c r="C91" s="13"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
+    <row r="91" spans="1:6">
       <c r="F91" s="11"/>
     </row>
-    <row r="92" spans="1:7">
-      <c r="C92" s="13"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
+    <row r="92" spans="1:6">
       <c r="F92" s="11"/>
     </row>
-    <row r="93" spans="1:7">
-      <c r="C93" s="13"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
+    <row r="93" spans="1:6">
       <c r="F93" s="11"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:6">
       <c r="F94" s="11"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:6">
       <c r="F95" s="11"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:6">
       <c r="F96" s="11"/>
     </row>
     <row r="97" spans="6:6">
@@ -3844,49 +3784,24 @@
       <c r="F109" s="11"/>
     </row>
     <row r="110" spans="6:6">
-      <c r="F110" s="11"/>
+      <c r="F110" s="14"/>
     </row>
     <row r="111" spans="6:6">
-      <c r="F111" s="11"/>
-    </row>
-    <row r="112" spans="6:6">
-      <c r="F112" s="11"/>
-    </row>
-    <row r="113" spans="6:6">
-      <c r="F113" s="11"/>
-    </row>
-    <row r="114" spans="6:6">
-      <c r="F114" s="14"/>
-    </row>
-    <row r="115" spans="6:6">
-      <c r="F115" s="14"/>
+      <c r="F111" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="D84:D86"/>
+    <mergeCell ref="E84:E86"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="D80:D82"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="D52:D54"/>
     <mergeCell ref="E52:E54"/>
@@ -3900,17 +3815,30 @@
     <mergeCell ref="C64:C66"/>
     <mergeCell ref="D64:D66"/>
     <mergeCell ref="C68:C70"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="D84:D86"/>
-    <mergeCell ref="E84:E86"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D4:D14 D16:D86 F35:F38 F40:F42 F44:F50 F52:F58 F60:F62 F64:F70 F72:F74 F76:F78 F80:F86">
@@ -3921,12 +3849,12 @@
       <formula>NOT(ISERROR(SEARCH(("Block / Skip"),(D4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F86 F114:F115">
+  <conditionalFormatting sqref="F3:F86 F110:F111">
     <cfRule type="notContainsBlanks" dxfId="4" priority="7">
       <formula>LEN(TRIM(F3))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F97">
+  <conditionalFormatting sqref="F3:F93">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Low"</formula>
     </cfRule>
@@ -3943,7 +3871,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F3 F7 F11 F15 F19 F23 F27 F31 F35 F39 F43 F47 F51 F55 F59 F63 F67 F71 F75 F79 F83 F114:F115" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F3 F7 F11 F15 F19 F23 F27 F31 F35 F39 F43 F47 F51 F55 F59 F63 F67 F71 F75 F79 F83 F110:F111" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4 D8 D12 D16 D20 D24 D28 D32 D36 D40 D44 D48 D52 D56 D60 D64 D68 D72 D76 D80 D84" xr:uid="{00000000-0002-0000-0100-000001000000}">
